--- a/Modulo_3/Jugos.xlsx
+++ b/Modulo_3/Jugos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanvazquez/Documents/GitHub/TEC-IN2032/Modulo_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BA7755-14CF-D044-A97A-EB8CC67EB993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7132E689-12E7-534C-8CC4-8E09F9E1E39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{123D0A1B-D6BB-034E-B465-163B10EFD2C9}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Subgrupo</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>LatasNoConformes</t>
+  </si>
+  <si>
+    <t>nLatas</t>
   </si>
 </sst>
 </file>
@@ -429,255 +432,348 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA3CA3BC-214B-A04D-99F6-C03C477EB799}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
         <v>9</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C26">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
         <v>7</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
         <v>9</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C30">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
         <v>6</v>
+      </c>
+      <c r="C31">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
